--- a/artfynd/A 5476-2023 artfynd.xlsx
+++ b/artfynd/A 5476-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123400068</v>
       </c>
       <c r="B2" t="n">
-        <v>77694</v>
+        <v>77697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>123399598</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>123400140</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 5476-2023 artfynd.xlsx
+++ b/artfynd/A 5476-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123400068</v>
       </c>
       <c r="B2" t="n">
-        <v>77697</v>
+        <v>77699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>123399598</v>
       </c>
       <c r="B3" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>123400140</v>
       </c>
       <c r="B4" t="n">
-        <v>92236</v>
+        <v>92238</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 5476-2023 artfynd.xlsx
+++ b/artfynd/A 5476-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123400068</v>
       </c>
       <c r="B2" t="n">
-        <v>77699</v>
+        <v>77700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123399598</v>
+        <v>123400140</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
+        <v>92244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,28 +789,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En gammal fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123400140</v>
+        <v>123399598</v>
       </c>
       <c r="B4" t="n">
-        <v>92238</v>
+        <v>78508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,33 +911,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
@@ -969,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En gammal fk</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5476-2023 artfynd.xlsx
+++ b/artfynd/A 5476-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123400068</v>
+        <v>123399598</v>
       </c>
       <c r="B2" t="n">
-        <v>77700</v>
+        <v>78511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396453</v>
+        <v>396640</v>
       </c>
       <c r="R2" t="n">
-        <v>6845332</v>
+        <v>6845024</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123400140</v>
+        <v>123400068</v>
       </c>
       <c r="B3" t="n">
-        <v>92244</v>
+        <v>77703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396640</v>
+        <v>396453</v>
       </c>
       <c r="R3" t="n">
-        <v>6845024</v>
+        <v>6845332</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,24 +860,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En gammal fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123399598</v>
+        <v>123400140</v>
       </c>
       <c r="B4" t="n">
-        <v>78508</v>
+        <v>92247</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,28 +901,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En gammal fk</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5476-2023 artfynd.xlsx
+++ b/artfynd/A 5476-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123399598</v>
+        <v>123400068</v>
       </c>
       <c r="B2" t="n">
-        <v>78511</v>
+        <v>77709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396640</v>
+        <v>396453</v>
       </c>
       <c r="R2" t="n">
-        <v>6845024</v>
+        <v>6845332</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123400068</v>
+        <v>123399598</v>
       </c>
       <c r="B3" t="n">
-        <v>77703</v>
+        <v>78517</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396453</v>
+        <v>396640</v>
       </c>
       <c r="R3" t="n">
-        <v>6845332</v>
+        <v>6845024</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,9 +850,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>123400140</v>
       </c>
       <c r="B4" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 5476-2023 artfynd.xlsx
+++ b/artfynd/A 5476-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123400068</v>
+        <v>123400140</v>
       </c>
       <c r="B2" t="n">
-        <v>77709</v>
+        <v>92269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396453</v>
+        <v>396640</v>
       </c>
       <c r="R2" t="n">
-        <v>6845332</v>
+        <v>6845024</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +753,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En gammal fk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123399598</v>
+        <v>123400068</v>
       </c>
       <c r="B3" t="n">
-        <v>78517</v>
+        <v>77714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396640</v>
+        <v>396453</v>
       </c>
       <c r="R3" t="n">
-        <v>6845024</v>
+        <v>6845332</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +870,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123400140</v>
+        <v>123399598</v>
       </c>
       <c r="B4" t="n">
-        <v>92264</v>
+        <v>78522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,33 +911,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
@@ -969,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En gammal fk</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5476-2023 artfynd.xlsx
+++ b/artfynd/A 5476-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123400140</v>
       </c>
       <c r="B2" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>123400068</v>
       </c>
       <c r="B3" t="n">
-        <v>77714</v>
+        <v>77716</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>123399598</v>
       </c>
       <c r="B4" t="n">
-        <v>78522</v>
+        <v>78524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
